--- a/PPU_UFA_ZAVODY_SPEC.xlsx
+++ b/PPU_UFA_ZAVODY_SPEC.xlsx
@@ -493,24 +493,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,7 +519,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Цены — с сайтов заводов, октябрь 2026, с НДС, за 1 шт («от», не оферта). Пусто — цена только по запросу. Контакты — со страниц официальных сайтов, сверены в двух местах сайта.</t>
+          <t>Стоимость комплекта (9 шт: 108×3, 377×2, 426×3, 530×1) — по прайсам на сайтах заводов, октябрь 2026, с НДС, без доставки. Контакты — со страниц официальных сайтов, сверены в двух местах сайта.</t>
         </is>
       </c>
     </row>
@@ -550,55 +546,35 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>108×4,5 (3 шт), ₽/шт</t>
+          <t>Стоимость комплекта, ₽</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>377×8 (2 шт), ₽/шт</t>
+          <t>Телефон</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>426×8 (3 шт), ₽/шт</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>530×9 (1 шт), ₽/шт</t>
+          <t>Сайт</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>Комплект по сайту, ₽</t>
+          <t>Где проверен контакт</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Телефон</t>
+          <t>Отправлен запрос (дата)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>Сайт</t>
-        </is>
-      </c>
-      <c r="M3" s="13" t="inlineStr">
-        <is>
-          <t>Где проверен контакт</t>
-        </is>
-      </c>
-      <c r="N3" s="13" t="inlineStr">
-        <is>
-          <t>Отправлен запрос (дата)</t>
-        </is>
-      </c>
-      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Ответ / цена КП</t>
         </is>
@@ -622,42 +598,30 @@
         <v>1300</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>6907.4</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>53598.4</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>55110.3</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>91102.7</v>
-      </c>
-      <c r="I4" s="8" t="n">
         <v>384352.6</v>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>+7 (4852) 91-96-10; +7 (4852) 91-96-22</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>info@pkfteplo.ru</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>ppu76.ru</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>сайт ppu76.ru, 23.10.2026: шапка и подвал главной</t>
         </is>
       </c>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -675,42 +639,30 @@
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="8" t="n">
-        <v>7587</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>55458</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>60393</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>99441</v>
-      </c>
-      <c r="I5" s="8" t="n">
         <v>414297</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>8 (800) 600-52-04</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>zakaz@proftehnoplast.ru</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>proftehnoplast.ru</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>сайт, 23.10.2026: главная страница (страница контактов не открылась)</t>
         </is>
       </c>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -730,42 +682,30 @@
         <v>525</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>10222</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>63274</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>72561</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>107789</v>
-      </c>
-      <c r="I6" s="8" t="n">
         <v>482686</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>+7 (343) 383-26-98</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>sale@saverhot.ru</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>saverhot.ru</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>сайт, 23.10.2026: главная и стр. /contacts/ совпадают</t>
         </is>
       </c>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -784,39 +724,33 @@
       <c r="D7" s="5" t="n">
         <v>950</v>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n">
-        <v>44743</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>54422</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>82733</v>
-      </c>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>+7 (831) 231-25-02 (отдел продаж); +7 (831) 231-25-01 (многоканальный)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>sale@1nzti.ru</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>https://1nzti.ru</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Телефоны и e-mail совпадают на стр. /contact/, в шапке/подвале главной и на каждой карточке товара (tel:+78312312502, mailto:sale@1nzti.ru)</t>
         </is>
       </c>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -835,35 +769,33 @@
       <c r="D8" s="5" t="n">
         <v>2050</v>
       </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n">
-        <v>103982</v>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 324-22-44</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>zavod@zti-ppu.ru</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>https://zti-ppu.ru</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>+7 812 324-22-44 и zavod@zti-ppu.ru — в шапке стр. отводов и на стр. /contact (tel:+78123242244 ×2, mailto:zavod@ ×4)</t>
         </is>
       </c>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -882,33 +814,33 @@
       <c r="D9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>(347) 246-33-58; (347) 246-49-98; отдел продаж +7 905 309-07-58</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>info@utzavod.ru</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>http://utzavod.ru</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Телефоны и e-mail совпадают на странице контактов, на главной и в подвале разделов «Трубы ППУ» и «Фасонные изделия»</t>
         </is>
       </c>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -927,33 +859,33 @@
       <c r="D10" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>+7 (495) 988-54-82</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>info@mosflowline.ru</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>https://www.mosflowline.ru</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Телефон и e-mail совпадают на стр. контактов и на главной (tel:+74959885482, mailto:info@mosflowline.ru)</t>
         </is>
       </c>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -972,33 +904,33 @@
       <c r="D11" s="5" t="n">
         <v>1400</v>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>+7 (499) 553-03-83</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>sales@t-ik.ru; info@t-ik.ru</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>https://t-ik.ru</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>+7 (499) 553-03-83 — главная (шапка) и стр. контактов; e-mail со стр. контактов</t>
         </is>
       </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -1017,33 +949,33 @@
       <c r="D12" s="5" t="n">
         <v>1680</v>
       </c>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>8-800-100-65-46 (бесплатный по РФ); Москва +7 (499) 404-20-98; ПФО — рук. проектов Иванов Д.А. (Чебоксары)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>sales@smit.su (продажи), smit@smit.su (общий); ПФО: dmitriy.a.ivanov@smit.su</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>https://smit.su (домен smit-yartsevo.ru не резолвится — DNS ENOTFOUND)</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>8-800-100-65-46 совпадает в шапке, на стр. контактов (несколько регионов) и в подвале (tel:88001006546 ×8); sales@smit.su — на стр. контакто</t>
         </is>
       </c>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -1062,33 +994,33 @@
       <c r="D13" s="5" t="n">
         <v>375</v>
       </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>+7 (961) 943-85-85</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>info@озти.рф</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>https://озти.рф</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Совпадают на странице «Контакты», на главной и на странице «Отводы ППУ» (шапка/подвал)</t>
         </is>
       </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1107,33 +1039,33 @@
       <c r="D14" s="5" t="n">
         <v>430</v>
       </c>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>+7 922 724-84-05 (также +7 922 724-84-30; директор +7 982 323-68-61)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>chzit@mail.ru</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>https://chzit.ru</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>+7 922 724-84-05 и chzit@mail.ru совпадают на странице «Контакты», в шапке главной и раздела «Фасонные изделия ППУ»</t>
         </is>
       </c>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -1152,33 +1084,33 @@
       <c r="D15" s="5" t="n">
         <v>540</v>
       </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>8 (800) 700-99-63; 8 (343) 305-63-00</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>ppu@azpt.ru</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>https://ppu.azpt.ru</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Совпадают на странице «Контакты» и в шапке/подвале главной (tel:88007009963, tel:83433056300, ppu@azpt.ru)</t>
         </is>
       </c>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -1197,33 +1129,33 @@
       <c r="D16" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>8 800 222-72-01</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>info@pzpt.ru</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>https://pzpt.ru</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Отдельной страницы «Контакты» нет (/kontakty/ и /contacts/ отдают 404). Телефон (4 tel-ссылки) и e-mail стоят в шапке и подвале страниц «Фас</t>
         </is>
       </c>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1242,33 +1174,33 @@
       <c r="D17" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>8 (800) 550-72-01</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>info@tduzti.com</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>https://tduzti.ru</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Телефон и e-mail совпадают на странице «Контакты» и на главной (3 tel-ссылки, mailto)</t>
         </is>
       </c>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1287,33 +1219,33 @@
       <c r="D18" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>8 800 222-72-30</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>info@teploset43.ru</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>https://saratov.teploset43.ru</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>8-800-222-72-30 и info@teploset43.ru совпадают на стр. контактов и на главной (tel:+78002227230, mailto:info@teploset43.ru)</t>
         </is>
       </c>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1332,38 +1264,38 @@
       <c r="D19" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>по запросу</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>8 (904) 494-05-59</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>oreon1963@mail.ru</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>https://tpsever.com</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Телефон и e-mail в шапке и подвале главной и раздела «Фасонные части»; /contacts отдаёт 404 (контакты в блоке на главной)</t>
         </is>
       </c>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>108: у НЗТИ и НИК на сайте только стенка 4,0 / 5,0 мм (в ТЗ 4,5) — цену не ставим, запросить 108×4,5. Комплект считается, только если есть цены на все 4 позиции.</t>
+          <t>«По запросу» — на сайте нет цен на все 4 позиции (у НЗТИ и НИК нет 108×4,5 — в ТЗ стенка 4,5 мм).</t>
         </is>
       </c>
     </row>
@@ -1383,9 +1315,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="A21:O21"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A23:K23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/PPU_UFA_ZAVODY_SPEC.xlsx
+++ b/PPU_UFA_ZAVODY_SPEC.xlsx
@@ -493,20 +493,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,7 +518,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Стоимость комплекта (9 шт: 108×3, 377×2, 426×3, 530×1) — по прайсам на сайтах заводов, октябрь 2026, с НДС, без доставки. Контакты — со страниц официальных сайтов, сверены в двух местах сайта.</t>
+          <t>Контакты — со страниц официальных сайтов, сверены в двух местах сайта.</t>
         </is>
       </c>
     </row>
@@ -546,37 +545,32 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Стоимость комплекта, ₽</t>
+          <t>Телефон</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Телефон</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Сайт</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>Сайт</t>
+          <t>Где проверен контакт</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>Где проверен контакт</t>
+          <t>Отправлен запрос (дата)</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Отправлен запрос (дата)</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>Ответ / цена КП</t>
+          <t>Ответ</t>
         </is>
       </c>
     </row>
@@ -597,31 +591,28 @@
       <c r="D4" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>384352.6</v>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+7 (4852) 91-96-10; +7 (4852) 91-96-22</t>
+        </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>+7 (4852) 91-96-10; +7 (4852) 91-96-22</t>
+          <t>info@pkfteplo.ru</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>info@pkfteplo.ru</t>
+          <t>ppu76.ru</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>ppu76.ru</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
           <t>сайт ppu76.ru, 23.10.2026: шапка и подвал главной</t>
         </is>
       </c>
+      <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -638,31 +629,28 @@
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="n">
-        <v>414297</v>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>8 (800) 600-52-04</t>
+        </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>8 (800) 600-52-04</t>
+          <t>zakaz@proftehnoplast.ru</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>zakaz@proftehnoplast.ru</t>
+          <t>proftehnoplast.ru</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>proftehnoplast.ru</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
           <t>сайт, 23.10.2026: главная страница (страница контактов не открылась)</t>
         </is>
       </c>
+      <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -681,31 +669,28 @@
       <c r="D6" s="5" t="n">
         <v>525</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>482686</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 383-26-98</t>
+        </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>+7 (343) 383-26-98</t>
+          <t>sale@saverhot.ru</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>sale@saverhot.ru</t>
+          <t>saverhot.ru</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>saverhot.ru</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
           <t>сайт, 23.10.2026: главная и стр. /contacts/ совпадают</t>
         </is>
       </c>
+      <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -724,33 +709,28 @@
       <c r="D7" s="5" t="n">
         <v>950</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+7 (831) 231-25-02 (отдел продаж); +7 (831) 231-25-01 (многоканальный)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>+7 (831) 231-25-02 (отдел продаж); +7 (831) 231-25-01 (многоканальный)</t>
+          <t>sale@1nzti.ru</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>sale@1nzti.ru</t>
+          <t>https://1nzti.ru</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>https://1nzti.ru</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
           <t>Телефоны и e-mail совпадают на стр. /contact/, в шапке/подвале главной и на каждой карточке товара (tel:+78312312502, mailto:sale@1nzti.ru)</t>
         </is>
       </c>
+      <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -769,33 +749,28 @@
       <c r="D8" s="5" t="n">
         <v>2050</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 324-22-44</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 324-22-44</t>
+          <t>zavod@zti-ppu.ru</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>zavod@zti-ppu.ru</t>
+          <t>https://zti-ppu.ru</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>https://zti-ppu.ru</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
           <t>+7 812 324-22-44 и zavod@zti-ppu.ru — в шапке стр. отводов и на стр. /contact (tel:+78123242244 ×2, mailto:zavod@ ×4)</t>
         </is>
       </c>
+      <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -814,33 +789,28 @@
       <c r="D9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>(347) 246-33-58; (347) 246-49-98; отдел продаж +7 905 309-07-58</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>(347) 246-33-58; (347) 246-49-98; отдел продаж +7 905 309-07-58</t>
+          <t>info@utzavod.ru</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>info@utzavod.ru</t>
+          <t>http://utzavod.ru</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>http://utzavod.ru</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
           <t>Телефоны и e-mail совпадают на странице контактов, на главной и в подвале разделов «Трубы ППУ» и «Фасонные изделия»</t>
         </is>
       </c>
+      <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -859,33 +829,28 @@
       <c r="D10" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+7 (495) 988-54-82</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 988-54-82</t>
+          <t>info@mosflowline.ru</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>info@mosflowline.ru</t>
+          <t>https://www.mosflowline.ru</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>https://www.mosflowline.ru</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
           <t>Телефон и e-mail совпадают на стр. контактов и на главной (tel:+74959885482, mailto:info@mosflowline.ru)</t>
         </is>
       </c>
+      <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -904,33 +869,28 @@
       <c r="D11" s="5" t="n">
         <v>1400</v>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+7 (499) 553-03-83</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>+7 (499) 553-03-83</t>
+          <t>sales@t-ik.ru; info@t-ik.ru</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>sales@t-ik.ru; info@t-ik.ru</t>
+          <t>https://t-ik.ru</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>https://t-ik.ru</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
           <t>+7 (499) 553-03-83 — главная (шапка) и стр. контактов; e-mail со стр. контактов</t>
         </is>
       </c>
+      <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -949,33 +909,28 @@
       <c r="D12" s="5" t="n">
         <v>1680</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>8-800-100-65-46 (бесплатный по РФ); Москва +7 (499) 404-20-98; ПФО — рук. проектов Иванов Д.А. (Чебоксары)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>8-800-100-65-46 (бесплатный по РФ); Москва +7 (499) 404-20-98; ПФО — рук. проектов Иванов Д.А. (Чебоксары)</t>
+          <t>sales@smit.su (продажи), smit@smit.su (общий); ПФО: dmitriy.a.ivanov@smit.su</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>sales@smit.su (продажи), smit@smit.su (общий); ПФО: dmitriy.a.ivanov@smit.su</t>
+          <t>https://smit.su (домен smit-yartsevo.ru не резолвится — DNS ENOTFOUND)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>https://smit.su (домен smit-yartsevo.ru не резолвится — DNS ENOTFOUND)</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
           <t>8-800-100-65-46 совпадает в шапке, на стр. контактов (несколько регионов) и в подвале (tel:88001006546 ×8); sales@smit.su — на стр. контакто</t>
         </is>
       </c>
+      <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -994,33 +949,28 @@
       <c r="D13" s="5" t="n">
         <v>375</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+7 (961) 943-85-85</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>+7 (961) 943-85-85</t>
+          <t>info@озти.рф</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>info@озти.рф</t>
+          <t>https://озти.рф</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>https://озти.рф</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
           <t>Совпадают на странице «Контакты», на главной и на странице «Отводы ППУ» (шапка/подвал)</t>
         </is>
       </c>
+      <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1039,33 +989,28 @@
       <c r="D14" s="5" t="n">
         <v>430</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+7 922 724-84-05 (также +7 922 724-84-30; директор +7 982 323-68-61)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>+7 922 724-84-05 (также +7 922 724-84-30; директор +7 982 323-68-61)</t>
+          <t>chzit@mail.ru</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>chzit@mail.ru</t>
+          <t>https://chzit.ru</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>https://chzit.ru</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
           <t>+7 922 724-84-05 и chzit@mail.ru совпадают на странице «Контакты», в шапке главной и раздела «Фасонные изделия ППУ»</t>
         </is>
       </c>
+      <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -1084,33 +1029,28 @@
       <c r="D15" s="5" t="n">
         <v>540</v>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>8 (800) 700-99-63; 8 (343) 305-63-00</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>8 (800) 700-99-63; 8 (343) 305-63-00</t>
+          <t>ppu@azpt.ru</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ppu@azpt.ru</t>
+          <t>https://ppu.azpt.ru</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>https://ppu.azpt.ru</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
           <t>Совпадают на странице «Контакты» и в шапке/подвале главной (tel:88007009963, tel:83433056300, ppu@azpt.ru)</t>
         </is>
       </c>
+      <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -1129,33 +1069,28 @@
       <c r="D16" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>8 800 222-72-01</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>8 800 222-72-01</t>
+          <t>info@pzpt.ru</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>info@pzpt.ru</t>
+          <t>https://pzpt.ru</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>https://pzpt.ru</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
           <t>Отдельной страницы «Контакты» нет (/kontakty/ и /contacts/ отдают 404). Телефон (4 tel-ссылки) и e-mail стоят в шапке и подвале страниц «Фас</t>
         </is>
       </c>
+      <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1174,33 +1109,28 @@
       <c r="D17" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>8 (800) 550-72-01</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>8 (800) 550-72-01</t>
+          <t>info@tduzti.com</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>info@tduzti.com</t>
+          <t>https://tduzti.ru</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>https://tduzti.ru</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
           <t>Телефон и e-mail совпадают на странице «Контакты» и на главной (3 tel-ссылки, mailto)</t>
         </is>
       </c>
+      <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1219,33 +1149,28 @@
       <c r="D18" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>8 800 222-72-30</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>8 800 222-72-30</t>
+          <t>info@teploset43.ru</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>info@teploset43.ru</t>
+          <t>https://saratov.teploset43.ru</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>https://saratov.teploset43.ru</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
           <t>8-800-222-72-30 и info@teploset43.ru совпадают на стр. контактов и на главной (tel:+78002227230, mailto:info@teploset43.ru)</t>
         </is>
       </c>
+      <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1264,60 +1189,47 @@
       <c r="D19" s="5" t="n">
         <v>860</v>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>по запросу</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>8 (904) 494-05-59</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>8 (904) 494-05-59</t>
+          <t>oreon1963@mail.ru</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>oreon1963@mail.ru</t>
+          <t>https://tpsever.com</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>https://tpsever.com</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
           <t>Телефон и e-mail в шапке и подвале главной и раздела «Фасонные части»; /contacts отдаёт 404 (контакты в блоке на главной)</t>
         </is>
       </c>
+      <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>«По запросу» — на сайте нет цен на все 4 позиции (у НЗТИ и НИК нет 108×4,5 — в ТЗ стенка 4,5 мм).</t>
+          <t>НЗТИ: на карточках «Отвод ППУ ГОСТ 10704» — в запросе требовать крутоизогнутый отвод по ГОСТ 17375/17380 (как в ТЗ).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>НЗТИ: на карточках «Отвод ППУ ГОСТ 10704» — в запросе требовать крутоизогнутый отвод по ГОСТ 17375/17380 (как в ТЗ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
           <t>Спецификация для запроса — следующие листы: «Спецификация», «ТЗ дословно», «Документы к отгрузке».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A23:K23"/>
+  <mergeCells count="2">
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
